--- a/static/standards-correlations/Alaska_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Alaska_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$35</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Alaska CS Standards, June 2019</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Alaska CS Standards, June 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -713,7 +714,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Develop and apply criteria for systematic discovery of errors and strategies for correction in computing systems.</t>
+          <t>Develop and apply criteria for systematic introductory of errors and strategies for correction in computing systems.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -785,7 +786,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) traces a file to a remote server; Discovery Systems 9 covers protocols. Routers, addressing, and scalability are absent.</t>
+          <t>Ext 5.3F (Talking to a Server) traces a file to a remote server; Introductory Systems 9 covers protocols. Routers, addressing, and scalability are absent.</t>
         </is>
       </c>
     </row>
@@ -879,7 +880,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3G (Secret Messages / HTTPS) shows why a password sent over HTTP is exposed. Discovery Systems 10 covers phishing as an attack on the person.</t>
+          <t>Ext 5.3G (Secret Messages / HTTPS) shows why a password sent over HTTP is exposed. Introductory Systems 10 covers phishing as an attack on the person.</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2011,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>Discovery Coding 2 addresses how professionals spend their time; Ext 5.3H (Find the Community) surfaces real practitioner work; Ext 5.3D (Who's Left Out?) raises who gets access regardless of background.</t>
+          <t>Introductory Coding 2 addresses how professionals spend their time; Ext 5.3H (Find the Community) surfaces real practitioner work; Ext 5.3D (Who's Left Out?) raises who gets access regardless of background.</t>
         </is>
       </c>
     </row>
@@ -2044,6 +2045,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2088,7 +2090,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2102,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2212,6 +2214,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -2229,7 +2233,7 @@
 Standard statements are reproduced from the state standards document, with parenthetical example lists trimmed for readability.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 An earlier revision of this file scored lab FRONT MATTER ONLY (headings, descriptions, concept tags, objectives) and materially undercounted coverage. Those figures are superseded.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?' in the labs), or where the standard is only partly met. Cells citing 'Ext N.NL' identify the specific extension carrying the evidence, so a reviewer can verify placement and decide whether optional work counts for their purposes.</t>
         </is>
